--- a/artfynd/A 5344-2026 artfynd.xlsx
+++ b/artfynd/A 5344-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73968967</v>
+        <v>75016800</v>
       </c>
       <c r="B2" t="n">
-        <v>100763</v>
+        <v>103682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>222002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yxnanäs 200 m norra huset OSO, Sm</t>
+          <t>L4 Yxanäs östra gdn 100 m O, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F2e 4204. SOM: Actaea spicata. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 4F2e 4204. SOM: Viola mirabilis. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövbryn i åker,  mycket sparsam</t>
+          <t>Lövbryn, lundrest</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75016800</v>
+        <v>73968967</v>
       </c>
       <c r="B3" t="n">
-        <v>103191</v>
+        <v>101227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,7 +817,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>L4 Yxanäs östra gdn 100 m O, Sm</t>
+          <t>Yxnanäs 200 m norra huset OSO, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F2e 4204. SOM: Viola mirabilis. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 4F2e 4204. SOM: Actaea spicata. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Lövbryn, lundrest</t>
+          <t>Lövbryn i åker,  mycket sparsam</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 5344-2026 artfynd.xlsx
+++ b/artfynd/A 5344-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75016800</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73968967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>